--- a/employees_TX.xlsx
+++ b/employees_TX.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>Legal Name</t>
   </si>
@@ -49,15 +52,24 @@
     <t>Semi-Monthly</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>Yi</t>
   </si>
   <si>
+    <t>Lin</t>
+  </si>
+  <si>
+    <t>Zhiyu</t>
+  </si>
+  <si>
     <t>Fan</t>
   </si>
   <si>
+    <t>Ma</t>
+  </si>
+  <si>
+    <t>Zhou</t>
+  </si>
+  <si>
     <t>Active</t>
   </si>
   <si>
@@ -68,34 +80,22 @@
   </si>
   <si>
     <t>Receiving - Receiving</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Zhiyu</t>
-  </si>
-  <si>
-    <t>Zhou</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-9]M\/d\/yyyy"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,31 +118,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -221,7 +205,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -256,7 +239,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -291,16 +273,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -422,160 +408,145 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="9" width="26.75" customWidth="1"/>
-    <col min="10" max="10" width="26.77" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1">
+        <v>45692</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="1">
+        <v>46233</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="3">
-        <v>45692</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="G4" s="1">
+        <v>45698</v>
+      </c>
+      <c r="H4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="I4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="J4" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="3">
-        <v>45698</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>